--- a/10 - Atrib Rest 2025 Gov R2 Papis como peritos.xlsx
+++ b/10 - Atrib Rest 2025 Gov R2 Papis como peritos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maiap\OneDrive\Desktop\Desenvolvimento\Estudo_Atribuicoes_PCSP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95183571-0899-409C-B981-429AA5565EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB45AD6-E2FD-42C7-8F84-D9246B9AE943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E2F6A9B-94A3-41DD-92E9-2C4405031CDE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{9E2F6A9B-94A3-41DD-92E9-2C4405031CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Carreiras e Atribuicoes 2025 CC" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
     Junção de Perito Oficial Criminal</t>
       </text>
     </comment>
-    <comment ref="BE4" authorId="2" shapeId="0" xr:uid="{6C9300CE-079E-4D38-B083-218107BF4E11}">
+    <comment ref="AU4" authorId="2" shapeId="0" xr:uid="{6C9300CE-079E-4D38-B083-218107BF4E11}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -68,7 +68,7 @@
     Correção</t>
       </text>
     </comment>
-    <comment ref="BG4" authorId="3" shapeId="0" xr:uid="{3CAD8BC3-5E7F-4AC0-BCE6-91369E7BA637}">
+    <comment ref="AW4" authorId="3" shapeId="0" xr:uid="{3CAD8BC3-5E7F-4AC0-BCE6-91369E7BA637}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -76,7 +76,7 @@
     Correção</t>
       </text>
     </comment>
-    <comment ref="BI4" authorId="4" shapeId="0" xr:uid="{485EE174-C8A3-4D4A-812B-B2D87A5ED1AA}">
+    <comment ref="AY4" authorId="4" shapeId="0" xr:uid="{485EE174-C8A3-4D4A-812B-B2D87A5ED1AA}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -84,7 +84,7 @@
     Correções para perito e médico</t>
       </text>
     </comment>
-    <comment ref="BK4" authorId="5" shapeId="0" xr:uid="{0E99382F-19DE-49C3-AB28-F98BF8BBA437}">
+    <comment ref="BA4" authorId="5" shapeId="0" xr:uid="{0E99382F-19DE-49C3-AB28-F98BF8BBA437}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -92,7 +92,7 @@
     Correção</t>
       </text>
     </comment>
-    <comment ref="BL4" authorId="6" shapeId="0" xr:uid="{958DFBB8-6931-4ED6-86D4-5D714673C33B}">
+    <comment ref="BB4" authorId="6" shapeId="0" xr:uid="{958DFBB8-6931-4ED6-86D4-5D714673C33B}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -108,7 +108,7 @@
     Junção do Papi e Auxi de forma simplista, sem atenção a legislação ou problemas jurídicos</t>
       </text>
     </comment>
-    <comment ref="AB5" authorId="8" shapeId="0" xr:uid="{C18DC59B-CF76-417E-9476-E363613D3A60}">
+    <comment ref="R5" authorId="8" shapeId="0" xr:uid="{C18DC59B-CF76-417E-9476-E363613D3A60}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -116,7 +116,7 @@
     Manutenção da ausência explícita</t>
       </text>
     </comment>
-    <comment ref="AC5" authorId="9" shapeId="0" xr:uid="{B337F473-5EA8-4E0A-8DC4-799480371A70}">
+    <comment ref="S5" authorId="9" shapeId="0" xr:uid="{B337F473-5EA8-4E0A-8DC4-799480371A70}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -124,7 +124,7 @@
     Remoção da atribuição de papi e auxi</t>
       </text>
     </comment>
-    <comment ref="AE5" authorId="10" shapeId="0" xr:uid="{DC2ACDCA-F0C9-4DFE-BC2F-DA63E8D7DB7A}">
+    <comment ref="U5" authorId="10" shapeId="0" xr:uid="{DC2ACDCA-F0C9-4DFE-BC2F-DA63E8D7DB7A}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -132,7 +132,7 @@
     Manutenção do ausência corretiva</t>
       </text>
     </comment>
-    <comment ref="AF5" authorId="11" shapeId="0" xr:uid="{A50E056E-12EC-4466-9765-59301526AFA4}">
+    <comment ref="V5" authorId="11" shapeId="0" xr:uid="{A50E056E-12EC-4466-9765-59301526AFA4}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -140,7 +140,7 @@
     Manutenção do ausência corretiva</t>
       </text>
     </comment>
-    <comment ref="AM5" authorId="12" shapeId="0" xr:uid="{3A7387E0-C332-4CAB-95F9-72E9DF72B009}">
+    <comment ref="AC5" authorId="12" shapeId="0" xr:uid="{3A7387E0-C332-4CAB-95F9-72E9DF72B009}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -148,7 +148,7 @@
     Remoção dessa atribuição</t>
       </text>
     </comment>
-    <comment ref="AN5" authorId="13" shapeId="0" xr:uid="{B2B0348D-F815-4854-BDB4-531627FD1AB2}">
+    <comment ref="AD5" authorId="13" shapeId="0" xr:uid="{B2B0348D-F815-4854-BDB4-531627FD1AB2}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -156,7 +156,7 @@
     Manutenção da ausência corretiva</t>
       </text>
     </comment>
-    <comment ref="BD5" authorId="14" shapeId="0" xr:uid="{B57F8026-66E5-42E1-A5AE-5910C1522650}">
+    <comment ref="AT5" authorId="14" shapeId="0" xr:uid="{B57F8026-66E5-42E1-A5AE-5910C1522650}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -164,7 +164,7 @@
     Junção simples de papi e auxiliar, sem respeitar as atribuições periciais</t>
       </text>
     </comment>
-    <comment ref="BI5" authorId="15" shapeId="0" xr:uid="{0DF6BF77-93F0-43C6-99CD-AFF3010E7B7E}">
+    <comment ref="AY5" authorId="15" shapeId="0" xr:uid="{0DF6BF77-93F0-43C6-99CD-AFF3010E7B7E}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -172,7 +172,7 @@
     Manutenção da ausência corretiva</t>
       </text>
     </comment>
-    <comment ref="BL5" authorId="16" shapeId="0" xr:uid="{38EBA2FE-3935-4807-997B-E8B6EA23D511}">
+    <comment ref="BB5" authorId="16" shapeId="0" xr:uid="{38EBA2FE-3935-4807-997B-E8B6EA23D511}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -188,7 +188,7 @@
     Junção do Agente de Telecomunicações, Agente Policial e Carcereiro Policial</t>
       </text>
     </comment>
-    <comment ref="AG6" authorId="18" shapeId="0" xr:uid="{26FBF889-DC53-46AA-8CCB-4505CA1772C0}">
+    <comment ref="W6" authorId="18" shapeId="0" xr:uid="{26FBF889-DC53-46AA-8CCB-4505CA1772C0}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -209,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>mediar conflitos</t>
   </si>
@@ -380,36 +380,6 @@
   </si>
   <si>
     <t>Delegado de Polícia</t>
-  </si>
-  <si>
-    <t>portar arma, distintivo e algemas</t>
-  </si>
-  <si>
-    <t>atender sempre, com urbanidade e eficiência, o público em geral, pessoalmente ou por telefone</t>
-  </si>
-  <si>
-    <t>elaborar, sob orientação da Autoridade Policial, registro de ocorrência</t>
-  </si>
-  <si>
-    <t>conduzir viatura policial</t>
-  </si>
-  <si>
-    <t>cumprir diligência e/ou requisição determinada pela Autoridade Policial, elaborando relatório respectivo</t>
-  </si>
-  <si>
-    <t>proceder à abordagem de pessoas suspeitas da prática de ilícitos, realizando busca pessoal quando necessário</t>
-  </si>
-  <si>
-    <t>identificar pessoas, inclusive por meio digital, nas hipóteses em que tal providência se faça necessária</t>
-  </si>
-  <si>
-    <t>conduzir e apresentar pessoas legalmente presas à Autoridade Policial competente ou onde for por ela determinado</t>
-  </si>
-  <si>
-    <t>auxiliar a Autoridade Policial na formalização de atos de polícia judiciária</t>
-  </si>
-  <si>
-    <t>operar os sistemas de comunicação e de dados da Polícia Civil</t>
   </si>
   <si>
     <t>gestão de polícia judiciária</t>
@@ -1363,55 +1333,55 @@
   <threadedComment ref="A4" dT="2026-08-15T16:10:41.59" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{7A845D24-CDD9-4399-BE6B-FEE17072A9C3}">
     <text>Junção de Perito Oficial Criminal</text>
   </threadedComment>
-  <threadedComment ref="BE4" dT="2024-11-21T15:31:54.55" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{6C9300CE-079E-4D38-B083-218107BF4E11}">
+  <threadedComment ref="AU4" dT="2024-11-21T15:31:54.55" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{6C9300CE-079E-4D38-B083-218107BF4E11}">
     <text>Correção</text>
   </threadedComment>
-  <threadedComment ref="BG4" dT="2024-11-21T15:32:15.77" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{3CAD8BC3-5E7F-4AC0-BCE6-91369E7BA637}">
+  <threadedComment ref="AW4" dT="2024-11-21T15:32:15.77" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{3CAD8BC3-5E7F-4AC0-BCE6-91369E7BA637}">
     <text>Correção</text>
   </threadedComment>
-  <threadedComment ref="BI4" dT="2024-11-21T15:32:56.32" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{485EE174-C8A3-4D4A-812B-B2D87A5ED1AA}">
+  <threadedComment ref="AY4" dT="2024-11-21T15:32:56.32" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{485EE174-C8A3-4D4A-812B-B2D87A5ED1AA}">
     <text>Correções para perito e médico</text>
   </threadedComment>
-  <threadedComment ref="BK4" dT="2024-11-21T15:34:36.24" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{0E99382F-19DE-49C3-AB28-F98BF8BBA437}">
+  <threadedComment ref="BA4" dT="2024-11-21T15:34:36.24" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{0E99382F-19DE-49C3-AB28-F98BF8BBA437}">
     <text>Correção</text>
   </threadedComment>
-  <threadedComment ref="BL4" dT="2024-11-21T15:35:00.67" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{958DFBB8-6931-4ED6-86D4-5D714673C33B}">
+  <threadedComment ref="BB4" dT="2024-11-21T15:35:00.67" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{958DFBB8-6931-4ED6-86D4-5D714673C33B}">
     <text>Correção</text>
   </threadedComment>
   <threadedComment ref="A5" dT="2024-11-21T15:21:50.13" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{18B51900-6C31-4041-8E3B-A44E68062E5E}">
     <text>Junção do Papi e Auxi de forma simplista, sem atenção a legislação ou problemas jurídicos</text>
   </threadedComment>
-  <threadedComment ref="AB5" dT="2024-11-21T15:17:29.11" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{C18DC59B-CF76-417E-9476-E363613D3A60}">
+  <threadedComment ref="R5" dT="2024-11-21T15:17:29.11" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{C18DC59B-CF76-417E-9476-E363613D3A60}">
     <text>Manutenção da ausência explícita</text>
   </threadedComment>
-  <threadedComment ref="AC5" dT="2024-11-21T15:20:22.28" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{B337F473-5EA8-4E0A-8DC4-799480371A70}">
+  <threadedComment ref="S5" dT="2024-11-21T15:20:22.28" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{B337F473-5EA8-4E0A-8DC4-799480371A70}">
     <text>Remoção da atribuição de papi e auxi</text>
   </threadedComment>
-  <threadedComment ref="AE5" dT="2024-11-21T15:22:43.30" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{DC2ACDCA-F0C9-4DFE-BC2F-DA63E8D7DB7A}">
+  <threadedComment ref="U5" dT="2024-11-21T15:22:43.30" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{DC2ACDCA-F0C9-4DFE-BC2F-DA63E8D7DB7A}">
     <text>Manutenção do ausência corretiva</text>
   </threadedComment>
-  <threadedComment ref="AF5" dT="2024-11-21T15:19:24.21" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{A50E056E-12EC-4466-9765-59301526AFA4}">
+  <threadedComment ref="V5" dT="2024-11-21T15:19:24.21" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{A50E056E-12EC-4466-9765-59301526AFA4}">
     <text>Manutenção do ausência corretiva</text>
   </threadedComment>
-  <threadedComment ref="AM5" dT="2024-11-21T15:14:14.60" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{3A7387E0-C332-4CAB-95F9-72E9DF72B009}">
+  <threadedComment ref="AC5" dT="2024-11-21T15:14:14.60" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{3A7387E0-C332-4CAB-95F9-72E9DF72B009}">
     <text>Remoção dessa atribuição</text>
   </threadedComment>
-  <threadedComment ref="AN5" dT="2024-11-21T15:29:59.76" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{B2B0348D-F815-4854-BDB4-531627FD1AB2}">
+  <threadedComment ref="AD5" dT="2024-11-21T15:29:59.76" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{B2B0348D-F815-4854-BDB4-531627FD1AB2}">
     <text>Manutenção da ausência corretiva</text>
   </threadedComment>
-  <threadedComment ref="BD5" dT="2024-11-21T15:15:18.16" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{B57F8026-66E5-42E1-A5AE-5910C1522650}">
+  <threadedComment ref="AT5" dT="2024-11-21T15:15:18.16" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{B57F8026-66E5-42E1-A5AE-5910C1522650}">
     <text>Junção simples de papi e auxiliar, sem respeitar as atribuições periciais</text>
   </threadedComment>
-  <threadedComment ref="BI5" dT="2024-11-21T15:33:18.68" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{0DF6BF77-93F0-43C6-99CD-AFF3010E7B7E}">
+  <threadedComment ref="AY5" dT="2024-11-21T15:33:18.68" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{0DF6BF77-93F0-43C6-99CD-AFF3010E7B7E}">
     <text>Manutenção da ausência corretiva</text>
   </threadedComment>
-  <threadedComment ref="BL5" dT="2024-11-21T15:35:09.16" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{38EBA2FE-3935-4807-997B-E8B6EA23D511}">
+  <threadedComment ref="BB5" dT="2024-11-21T15:35:09.16" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{38EBA2FE-3935-4807-997B-E8B6EA23D511}">
     <text>Correção ainda proposta</text>
   </threadedComment>
   <threadedComment ref="A6" dT="2024-11-21T15:19:03.44" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{5762A027-CB49-43DA-8C73-259A304EF72E}">
     <text>Junção do Agente de Telecomunicações, Agente Policial e Carcereiro Policial</text>
   </threadedComment>
-  <threadedComment ref="AG6" dT="2024-11-21T15:25:58.48" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{26FBF889-DC53-46AA-8CCB-4505CA1772C0}">
+  <threadedComment ref="W6" dT="2024-11-21T15:25:58.48" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{26FBF889-DC53-46AA-8CCB-4505CA1772C0}">
     <text>Manutenção da ausência corretiva</text>
   </threadedComment>
   <threadedComment ref="A7" dT="2024-11-21T15:37:26.07" personId="{FD87976F-6E2D-48CA-AE66-3D132C3F2D7E}" id="{7F787235-CCEF-4E3A-84DC-CF8051E8B649}">
@@ -1422,62 +1392,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61E66DEB-712A-465C-882E-F5424BC162B6}">
-  <dimension ref="A1:BU7"/>
+  <dimension ref="A1:BK7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="46" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="55" max="56" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="8" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="69" max="71" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="36" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="8" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="59" max="61" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" s="1" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:63" s="1" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>57</v>
@@ -1489,214 +1449,184 @@
         <v>59</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="N1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T1" s="3" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="BF1" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="BL1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="BM1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BN1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="BO1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="BP1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="BQ1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="BR1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="BS1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="BT1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="BU1" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>56</v>
       </c>
@@ -1713,34 +1643,34 @@
         <v>1</v>
       </c>
       <c r="F2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="5">
         <v>0</v>
@@ -1851,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="AZ2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA2" s="5">
         <v>0</v>
@@ -1881,57 +1811,27 @@
         <v>0</v>
       </c>
       <c r="BJ2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK2" s="5">
         <v>0</v>
       </c>
-      <c r="BL2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU2" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="5">
         <v>1</v>
@@ -1952,49 +1852,49 @@
         <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="5">
         <v>1</v>
       </c>
       <c r="Q3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="5">
         <v>0</v>
@@ -2072,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="AZ3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA3" s="5">
         <v>0</v>
@@ -2102,75 +2002,45 @@
         <v>0</v>
       </c>
       <c r="BJ3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK3" s="5">
         <v>0</v>
       </c>
-      <c r="BL3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU3" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
         <v>0</v>
@@ -2188,34 +2058,34 @@
         <v>0</v>
       </c>
       <c r="Q4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="5">
         <v>1</v>
@@ -2245,79 +2115,79 @@
         <v>1</v>
       </c>
       <c r="AJ4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT4" s="5">
         <v>0</v>
       </c>
       <c r="AU4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV4" s="5">
         <v>0</v>
       </c>
       <c r="AW4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE4" s="5">
         <v>1</v>
       </c>
       <c r="BF4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI4" s="5">
         <v>1</v>
@@ -2328,70 +2198,40 @@
       <c r="BK4" s="5">
         <v>1</v>
       </c>
-      <c r="BL4" s="5">
-        <v>1</v>
-      </c>
-      <c r="BM4" s="5">
-        <v>1</v>
-      </c>
-      <c r="BN4" s="5">
-        <v>1</v>
-      </c>
-      <c r="BO4" s="5">
-        <v>1</v>
-      </c>
-      <c r="BP4" s="5">
-        <v>1</v>
-      </c>
-      <c r="BQ4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS4" s="5">
-        <v>1</v>
-      </c>
-      <c r="BT4" s="5">
-        <v>1</v>
-      </c>
-      <c r="BU4" s="5">
-        <v>1</v>
-      </c>
     </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -2412,22 +2252,22 @@
         <v>0</v>
       </c>
       <c r="R5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" s="5">
         <v>0</v>
@@ -2442,55 +2282,55 @@
         <v>0</v>
       </c>
       <c r="AB5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="5">
         <v>1</v>
       </c>
       <c r="AE5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="5">
         <v>0</v>
       </c>
       <c r="AI5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" s="5">
         <v>1</v>
       </c>
       <c r="AO5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="5">
         <v>1</v>
@@ -2499,16 +2339,16 @@
         <v>1</v>
       </c>
       <c r="AU5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY5" s="5">
         <v>1</v>
@@ -2517,16 +2357,16 @@
         <v>1</v>
       </c>
       <c r="BA5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB5" s="5">
         <v>1</v>
       </c>
       <c r="BC5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE5" s="5">
         <v>0</v>
@@ -2541,69 +2381,39 @@
         <v>0</v>
       </c>
       <c r="BI5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK5" s="5">
         <v>0</v>
       </c>
-      <c r="BL5" s="5">
-        <v>1</v>
-      </c>
-      <c r="BM5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU5" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <v>1</v>
@@ -2615,19 +2425,19 @@
         <v>1</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="5">
         <v>0</v>
@@ -2636,28 +2446,28 @@
         <v>0</v>
       </c>
       <c r="S6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="5">
         <v>0</v>
@@ -2735,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="AZ6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA6" s="5">
         <v>0</v>
@@ -2765,75 +2575,45 @@
         <v>0</v>
       </c>
       <c r="BJ6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK6" s="5">
         <v>0</v>
       </c>
-      <c r="BL6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU6" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
         <v>0</v>
@@ -2869,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="W7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" s="5">
         <v>0</v>
@@ -2884,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7" s="5">
         <v>0</v>
@@ -2899,13 +2679,13 @@
         <v>0</v>
       </c>
       <c r="AG7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="5">
         <v>0</v>
       </c>
       <c r="AI7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="5">
         <v>0</v>
@@ -2914,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="AL7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM7" s="5">
         <v>0</v>
@@ -2935,40 +2715,40 @@
         <v>0</v>
       </c>
       <c r="AS7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT7" s="5">
         <v>0</v>
       </c>
       <c r="AU7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE7" s="5">
         <v>1</v>
@@ -2989,41 +2769,11 @@
         <v>1</v>
       </c>
       <c r="BK7" s="5">
-        <v>1</v>
-      </c>
-      <c r="BL7" s="5">
-        <v>1</v>
-      </c>
-      <c r="BM7" s="5">
-        <v>1</v>
-      </c>
-      <c r="BN7" s="5">
-        <v>1</v>
-      </c>
-      <c r="BO7" s="5">
-        <v>1</v>
-      </c>
-      <c r="BP7" s="5">
-        <v>1</v>
-      </c>
-      <c r="BQ7" s="5">
-        <v>1</v>
-      </c>
-      <c r="BR7" s="5">
-        <v>1</v>
-      </c>
-      <c r="BS7" s="5">
-        <v>1</v>
-      </c>
-      <c r="BT7" s="5">
-        <v>1</v>
-      </c>
-      <c r="BU7" s="5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:BU7">
+  <conditionalFormatting sqref="B2:BK7">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
